--- a/output/full_scan/batch_seq1_2026-10-07.xlsx
+++ b/output/full_scan/batch_seq1_2026-10-07.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1308</v>
+        <v>1303</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>962.5812621770758</v>
+        <v>1274.762367467295</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14.75</v>
+        <v>314</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>59.13991348237969</v>
+        <v>79.28990441366935</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>33.36179518569519</v>
+        <v>36.27914790550425</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.591293988792752</v>
+        <v>1.658387782758268</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0213719215472515</v>
+        <v>6.075103775481377</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1434</v>
+        <v>1301</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>944.3347493514171</v>
+        <v>1194.629245287513</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>18.95</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>66.00226007456087</v>
+        <v>74.41165206372825</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>24.97170264228419</v>
+        <v>27.45677589769597</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5.089760364598647</v>
+        <v>4.06292452875134</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.0681095706389535</v>
+        <v>0.6804152562858643</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1301</v>
+        <v>1504</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>914.6292452875134</v>
+        <v>1088.455222916632</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>74.41165205540572</v>
+        <v>63.99222818084615</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>27.45677592470904</v>
+        <v>14.39543556994877</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.06292452875134</v>
+        <v>4.941810115540318</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.6804152562858643</v>
+        <v>0.2930620908522919</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1455</v>
+        <v>1434</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>909</v>
+        <v>1079.334749351417</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10.8</v>
+        <v>18.95</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>70.8220136369743</v>
+        <v>66.00226005829427</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>29.276852343091</v>
+        <v>24.97170266743334</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>12.33364014064866</v>
+        <v>5.089760364598647</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0651811749388079</v>
+        <v>0.0681095706389535</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1326</v>
+        <v>1563</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>907.3266298593689</v>
+        <v>1073.377476809485</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>75.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>66.70752122353198</v>
+        <v>69.74851631666192</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>30.26955034198299</v>
+        <v>39.39575830136492</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.301976287431038</v>
+        <v>0.7782401475882975</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.5151615380953376</v>
+        <v>0.0824605212850047</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1315</v>
+        <v>1326</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>905.3330858031424</v>
+        <v>1067.326629859369</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>72</v>
+        <v>75.8</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>84.38675138196599</v>
+        <v>66.70752124661675</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45.3776045572132</v>
+        <v>30.26955040546524</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.544604530372204</v>
+        <v>2.301976287431038</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2492805755492008</v>
+        <v>0.5151615380730905</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1303</v>
+        <v>1513</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>869.7623674672949</v>
+        <v>1050.479474038258</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>79.28990440229248</v>
+        <v>55.7201630675337</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>36.27914786442336</v>
+        <v>9.004448202643866</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.658387782758268</v>
+        <v>1.668860253786032</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>6.075103775670547</v>
+        <v>0.1638666537015531</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1440</v>
+        <v>1455</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>846.9557436911941</v>
+        <v>1049</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13.95</v>
+        <v>10.8</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>59.58734070182116</v>
+        <v>70.8220136369743</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>13.97916936267326</v>
+        <v>29.27685237096814</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.957673582199248</v>
+        <v>12.33364014064866</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.037521972422341</v>
+        <v>0.0651811749388079</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1504</v>
+        <v>1315</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>838.4552229166321</v>
+        <v>1020.333085803142</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>73.3</v>
+        <v>72</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>63.99222824237473</v>
+        <v>84.38675140138922</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>14.39543560955511</v>
+        <v>45.37760460200952</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4.941810115540318</v>
+        <v>3.544604530372204</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2930620906297455</v>
+        <v>0.2492805755269521</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>823.5692040075945</v>
+        <v>982.581262177076</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>15.05</v>
+        <v>14.75</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>59.10581070439</v>
+        <v>59.13991356896133</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>41.33432482022067</v>
+        <v>33.36179525855633</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.18233027117531</v>
+        <v>1.591293988792752</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.0491349357797673</v>
+        <v>0.0213719215138709</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1563</v>
+        <v>1304</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>823.3774768094844</v>
+        <v>931.7885699660948</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>80.59999999999999</v>
+        <v>13.05</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>69.74851638003207</v>
+        <v>60.62802232287409</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>39.39575823840771</v>
+        <v>28.82124778624847</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.7782401475882975</v>
+        <v>2.344576391314734</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0824605212087301</v>
+        <v>0.0501101676877639</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1304</v>
+        <v>1560</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>811.7885699660948</v>
+        <v>898.1432707116265</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13.05</v>
+        <v>1020</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.62802222961287</v>
+        <v>74.55876489389027</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>28.82124776834167</v>
+        <v>48.56986735103972</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.344576391314734</v>
+        <v>0.4552635037207143</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.050110167732272</v>
+        <v>11.23787541411757</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1513</v>
+        <v>1305</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>770.479474038258</v>
+        <v>887.6842061698944</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>168</v>
+        <v>12.9</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>55.7201630308718</v>
+        <v>62.86519124528443</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>9.004448275694825</v>
+        <v>19.20673900159874</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.668860253786032</v>
+        <v>2.178338242327577</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.163866653590281</v>
+        <v>0.0676230001728656</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1101</v>
+        <v>1325</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>748.9807438309386</v>
+        <v>874.7713587971464</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>25.5</v>
+        <v>27.8</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>56.63331397745451</v>
+        <v>69.31605179498199</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>39.09679296443772</v>
+        <v>23.50636052910556</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.689772956196944</v>
+        <v>7.171782671247704</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0468553452787874</v>
+        <v>0.1814762816675907</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1305</v>
+        <v>1440</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>742.6842061698944</v>
+        <v>866.955743691194</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12.9</v>
+        <v>13.95</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>62.86519121401454</v>
+        <v>59.58734067837375</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>19.20673901291084</v>
+        <v>13.97916954240434</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2.178338242327577</v>
+        <v>2.957673582199248</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0676230001728656</v>
+        <v>0.0375219724779762</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1325</v>
+        <v>1569</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>734.7713587971463</v>
+        <v>847.9731985655321</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>27.8</v>
+        <v>72.2</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>69.31605181687448</v>
+        <v>81.55476174401926</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>23.50636050461431</v>
+        <v>62.17734397515126</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>7.171782671247704</v>
+        <v>1.397319856553209</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.1814762817120979</v>
+        <v>1.043679816367087</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1528</v>
+        <v>1312</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>702.6443685197744</v>
+        <v>843.5692040075945</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>24.05</v>
+        <v>15.05</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>55.10646979529781</v>
+        <v>59.10581071257359</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>38.43219111902847</v>
+        <v>41.33432482164648</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.1613179434997113</v>
+        <v>1.18233027117531</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.2492170098764043</v>
+        <v>-0.0491349357797673</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1313</v>
+        <v>1476</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>683.5557230184163</v>
+        <v>813.1692728486029</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>12.6</v>
+        <v>297</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>61.29303568534812</v>
+        <v>55.66879836740939</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>30.14041261569486</v>
+        <v>38.85347513400722</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.126311840141173</v>
+        <v>2.218979163279426</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.033891790585627</v>
+        <v>3.003069117592556</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1309</v>
+        <v>1477</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>654.0222466241953</v>
+        <v>811.020832236788</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>14.4</v>
+        <v>202.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>59.54243838067985</v>
+        <v>59.42704256994389</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>31.95578273729308</v>
+        <v>27.75993785373517</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.02455337879264</v>
+        <v>1.576544008717176</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0406735616298426</v>
+        <v>1.855804678131177</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1560</v>
+        <v>1101</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>648.1432707116265</v>
+        <v>748.9807438309386</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1020</v>
+        <v>25.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>74.55876490654832</v>
+        <v>56.63331073096542</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>48.56986745201134</v>
+        <v>39.09678960592658</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.4552635037207143</v>
+        <v>0.689772956196944</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>11.23787541389493</v>
+        <v>0.0468553505753025</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1569</v>
+        <v>1409</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>647.9731985655321</v>
+        <v>717.816445334383</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>72.2</v>
+        <v>26.15</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>81.55476167942145</v>
+        <v>62.20012681587318</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>62.17734397028665</v>
+        <v>17.9338066691653</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.397319856553209</v>
+        <v>2.081644533438309</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,11 +1630,11 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.043679816723158</v>
+        <v>0.1502472223824183</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>618.4845313540053</v>
+        <v>713.4845313540053</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>28.6</v>
@@ -1665,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>55.82359591411322</v>
+        <v>55.82359585506786</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>11.28878422485593</v>
@@ -1674,7 +1674,7 @@
         <v>1.046186596870981</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0172433563083647</v>
+        <v>0.0172433563751262</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1524</v>
+        <v>1313</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>589.8293101869009</v>
+        <v>703.5557230184163</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>26.1</v>
+        <v>12.6</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>46.39523668101136</v>
+        <v>61.29303568534812</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>30.95238821260936</v>
+        <v>30.14041259434211</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.699276148667236</v>
+        <v>1.126311840141173</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0238224702988802</v>
+        <v>0.0338917905967533</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, williams_r_recovery</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1477</v>
+        <v>1528</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>576.020832236788</v>
+        <v>702.6443685197744</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>202.5</v>
+        <v>24.05</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>59.42704270063259</v>
+        <v>55.10646972952446</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>27.7599377024405</v>
+        <v>38.43219112981244</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.576544008717176</v>
+        <v>0.1613179434997113</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,11 +1789,11 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.855804676573386</v>
+        <v>-0.2492170096538613</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>569.4631089482555</v>
+        <v>694.4631089482555</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>9.74</v>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>66.58171682123641</v>
+        <v>66.58171683179648</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>39.22954870532791</v>
+        <v>39.22954869768774</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.9468867054064894</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0929790517676799</v>
+        <v>0.0929790517765821</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1236</v>
+        <v>1309</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>568.3047144290417</v>
+        <v>674.0222466241953</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>25.8</v>
+        <v>14.4</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>58.21575285532995</v>
+        <v>59.54243839054637</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>18.45378997786281</v>
+        <v>31.95578275221545</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.828714335147378</v>
+        <v>1.02455337879264</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0004814602389544</v>
+        <v>0.0406735616298426</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1476</v>
+        <v>1524</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>560.6123960078315</v>
+        <v>609.8293101868998</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>297</v>
+        <v>26.1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>55.66879854104569</v>
+        <v>46.39523673357304</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>38.85347471698715</v>
+        <v>30.95238823788052</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2.01088058587947</v>
+        <v>1.699276148667236</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>3.003069112362848</v>
+        <v>0.023822470454661</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1323</v>
+        <v>1503</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>536.6142848342973</v>
+        <v>569.1151906356009</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>21.5</v>
+        <v>199.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.77054137032606</v>
+        <v>50.66852620188105</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15.24832996091777</v>
+        <v>8.410616345564549</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.5468091649178082</v>
+        <v>1.332300541392411</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.008266110118722801</v>
+        <v>0.2341836926437135</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1558</v>
+        <v>1236</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>535.5397973741884</v>
+        <v>568.3047144290417</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>109</v>
+        <v>25.8</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>53.40137886073057</v>
+        <v>58.21575282478576</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>37.49644341990592</v>
+        <v>18.45378997786281</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.2425417263962982</v>
+        <v>0.828714335147378</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.6751377928352795</v>
+        <v>0.0004814602389544</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1314</v>
+        <v>1216</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>527.2317857532323</v>
+        <v>558.5730284922184</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>8.91</v>
+        <v>75.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>57.97885343031747</v>
+        <v>53.92525877560313</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>41.06081746576204</v>
+        <v>13.37759010720919</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6007392112619582</v>
+        <v>1.630046483314159</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.0094512371772007</v>
+        <v>0.0169178707391631</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1568</v>
+        <v>1323</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>499.8851197468803</v>
+        <v>556.6142848342973</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>31.35</v>
+        <v>21.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>55.57534299404024</v>
+        <v>54.7705413463018</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>26.91674753748081</v>
+        <v>15.24832988707862</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.8922805392851046</v>
+        <v>0.5468091649178082</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0684593715465369</v>
+        <v>-0.008266110118722801</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1531</v>
+        <v>1558</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>499.8041873968062</v>
+        <v>555.5397973741884</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>11.5</v>
+        <v>109</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>40.90753472648074</v>
+        <v>53.40137892456934</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>20.06295970207045</v>
+        <v>37.49644351626163</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5099800355266373</v>
+        <v>0.2425417263962982</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.0063380238467785</v>
+        <v>-0.6751377928130191</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1409</v>
+        <v>1314</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>492.8164453343832</v>
+        <v>547.2317857532323</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>26.15</v>
+        <v>8.91</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>62.20012675847204</v>
+        <v>57.97885345834422</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>17.93380685884135</v>
+        <v>41.06081744344971</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2.081644533438309</v>
+        <v>0.6007392112619582</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1502472221932581</v>
+        <v>-0.0094512371861023</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1416</v>
+        <v>1445</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>481.8454998423289</v>
+        <v>544.6089949259077</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>11.85</v>
+        <v>10.4</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>62.31345160742617</v>
+        <v>57.25920580671306</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.66411276528702</v>
+        <v>16.35237220804006</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.8643710308045665</v>
+        <v>1.750549526758712</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0485056320076984</v>
+        <v>0.0412923236300775</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1338</v>
+        <v>1474</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>471.2727479304382</v>
+        <v>532.4235527942026</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>15.05</v>
+        <v>10</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>55.29057661237029</v>
+        <v>49.39720424058909</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>36.98579853748122</v>
+        <v>20.69605986200607</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.2592778274855414</v>
+        <v>3.342355279420258</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0718219539549779</v>
+        <v>0.0065243897629205</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1418</v>
+        <v>1102</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>465.7469962819297</v>
+        <v>532.0767755532281</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>18.6</v>
+        <v>35.9</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>61.50612641025345</v>
+        <v>59.29172739760979</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>34.4123630601144</v>
+        <v>22.58840217960634</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4206376372949958</v>
+        <v>0.7909727812287801</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.1083687890563773</v>
+        <v>-0.0307385991524343</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1103</v>
+        <v>1342</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>458.4223038308047</v>
+        <v>528.7363755455564</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>13.15</v>
+        <v>101</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>50.20325724691686</v>
+        <v>48.75497587768669</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>24.86358084841454</v>
+        <v>18.37315004460633</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.05848962528286</v>
+        <v>0.8892693463247854</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0055467596872436</v>
+        <v>0.1253745059923658</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1464</v>
+        <v>1568</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>454.5981328764257</v>
+        <v>519.8851197468803</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>9.94</v>
+        <v>31.35</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>40.75345192082253</v>
+        <v>55.57534296508327</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>23.18004376577655</v>
+        <v>26.91674764611362</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9359471246002996</v>
+        <v>0.8922805392851046</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0077652553668492</v>
+        <v>0.06845937157991649</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1444</v>
+        <v>1459</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>446.7530813650426</v>
+        <v>503.9388993628672</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>6.99</v>
+        <v>18.25</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>50.66673510880957</v>
+        <v>63.91172714650316</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>18.57864463271603</v>
+        <v>61.24883033917264</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.231057352857421</v>
+        <v>2.993889936286725</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.021413263807672</v>
+        <v>0.2715166589313162</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1216</v>
+        <v>1531</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>443.5730284922184</v>
+        <v>499.8041873968062</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>75.5</v>
+        <v>11.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>53.92525877560313</v>
+        <v>40.9075347594455</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>13.37759008176461</v>
+        <v>20.06295973933096</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.630046483314159</v>
+        <v>0.5099800355266373</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0169178706056329</v>
+        <v>0.0063380238245238</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1456</v>
+        <v>1218</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>439.7981548235828</v>
+        <v>499.0839483671159</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>14.4</v>
+        <v>14.45</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.07509860325438</v>
+        <v>49.2774957450382</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>21.91980641321643</v>
+        <v>4.252582128629161</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.3338418637670273</v>
+        <v>0.9027753538456168</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0186608766650631</v>
+        <v>0.0195024331783094</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1521</v>
+        <v>1470</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>438.1960820286801</v>
+        <v>497.2528191886439</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>25.7</v>
+        <v>24.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.33228670329338</v>
+        <v>52.25127150333345</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>31.88155567595458</v>
+        <v>8.965365567725579</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4842193835373774</v>
+        <v>0.1872232606178991</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.049958765053567</v>
+        <v>0.0104801895395749</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1514</v>
+        <v>1319</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>437.5009456301928</v>
+        <v>490.5250041286358</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>103.5</v>
+        <v>80</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>53.86207486932849</v>
+        <v>53.86281283862909</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>13.16983250506068</v>
+        <v>14.53676380771368</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.805627201420589</v>
+        <v>1.353802600455429</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2593914847227476</v>
+        <v>-0.0340977761399772</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1102</v>
+        <v>1416</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>437.0767755532281</v>
+        <v>481.8454998423289</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>35.9</v>
+        <v>11.85</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>59.29172753982629</v>
+        <v>62.31345153111781</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>22.58840213463797</v>
+        <v>17.66411276875398</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.7909727812287801</v>
+        <v>0.8643710308045665</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.0307385992192007</v>
+        <v>0.0485056320076984</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, cci_momentum, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1445</v>
+        <v>1533</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>434.6089949259077</v>
+        <v>480.2102463243023</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>10.4</v>
+        <v>30.55</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>57.25920566649864</v>
+        <v>45.95351442727091</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16.35237218118415</v>
+        <v>14.10011416531754</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.750549526758712</v>
+        <v>1.721063062002436</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0412923236523308</v>
+        <v>0.07546173222906589</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1447</v>
+        <v>1321</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>432.2093737497518</v>
+        <v>473.4184899433201</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>6.62</v>
+        <v>32.45</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>50.45766478642111</v>
+        <v>51.22830061852085</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>18.23698656829259</v>
+        <v>8.596622035147153</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.584571434013131</v>
+        <v>1.559556194460817</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.026238017021228</v>
+        <v>-0.0183178846522035</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1474</v>
+        <v>1338</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>422.4235527942026</v>
+        <v>471.2727479304382</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>10</v>
+        <v>15.05</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>49.39720445145156</v>
+        <v>55.29057654001555</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20.69605984384209</v>
+        <v>36.98579853748122</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>3.342355279420258</v>
+        <v>0.2592778274855414</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0065243897184137</v>
+        <v>0.07182195396610511</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1342</v>
+        <v>1418</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>418.7363755455564</v>
+        <v>465.7469962819297</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>101</v>
+        <v>18.6</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>48.75497592060832</v>
+        <v>61.50612725921303</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>18.37315006218566</v>
+        <v>34.41236329527521</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.8892693463247854</v>
+        <v>0.4206376372949958</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1253745059256015</v>
+        <v>0.1083687887225609</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1519</v>
+        <v>1307</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>414.7795064455548</v>
+        <v>461.9490822315731</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>702</v>
+        <v>31.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>47.7839354592698</v>
+        <v>59.02154345741307</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>11.94388663744685</v>
+        <v>12.7564045000357</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.770105206786588</v>
+        <v>0.8925828464004076</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.6803068042245037</v>
+        <v>0.1080275243864436</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1467</v>
+        <v>1103</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>403.514878698703</v>
+        <v>458.4223038308048</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>8.210000000000001</v>
+        <v>13.15</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.79791564311165</v>
+        <v>50.20325732302059</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>14.24138836097082</v>
+        <v>24.86358084841454</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.025422679737074</v>
+        <v>1.05848962528286</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0424425946920301</v>
+        <v>0.0055467596761168</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1439</v>
+        <v>1521</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>398.24404797791</v>
+        <v>458.1960820286795</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0</v>
+        <v>25.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>6.524392482279197</v>
+        <v>52.33228670329338</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>23.47364502444461</v>
+        <v>31.88155570698073</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.0005140823513192</v>
+        <v>0.4842193835373774</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.817468256452089</v>
+        <v>0.0499587650201854</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3230,21 +3230,21 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1339</v>
+        <v>1464</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>395.3913699803809</v>
+        <v>454.5981328764257</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>42.45</v>
+        <v>9.94</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>43.94046777956808</v>
+        <v>40.75345182171564</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>25.67834942917641</v>
+        <v>23.18004378002054</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.8072684378089459</v>
+        <v>0.9359471246002996</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0187135267472686</v>
+        <v>0.0077652553779774</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1218</v>
+        <v>1444</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>389.0839483671159</v>
+        <v>446.7530813650426</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>14.45</v>
+        <v>6.99</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>49.27749579323099</v>
+        <v>50.66673511424164</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>4.252582202671975</v>
+        <v>18.57864460824399</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9027753538456168</v>
+        <v>2.231057352857421</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0195024331560555</v>
+        <v>0.0214132638032214</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1470</v>
+        <v>1456</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>387.2528191886439</v>
+        <v>439.7981548235828</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>24.3</v>
+        <v>14.4</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>52.2512715062056</v>
+        <v>51.07509874328261</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>8.965365595462275</v>
+        <v>21.91980643778144</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.1872232606178991</v>
+        <v>0.3338418637670273</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0104801895395749</v>
+        <v>0.0186608765983011</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1340</v>
+        <v>1514</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>386.4005668189943</v>
+        <v>437.5009456301935</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>5.18</v>
+        <v>103.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.18655454786583</v>
+        <v>53.86207489406974</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>11.73592109082842</v>
+        <v>13.16983247338283</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.403427619630548</v>
+        <v>1.805627201420589</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0031444864755204</v>
+        <v>0.2593914847227476</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1220</v>
+        <v>1447</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>384.5795921759739</v>
+        <v>432.2093737497518</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>10.9</v>
+        <v>6.62</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>53.04305185053258</v>
+        <v>50.45766478642111</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>20.03170138532881</v>
+        <v>18.23698654909437</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5587576441062392</v>
+        <v>1.584571434013131</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0265520308529454</v>
+        <v>0.0262380170123263</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1319</v>
+        <v>1519</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>380.5250041286358</v>
+        <v>414.7795064455549</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>80</v>
+        <v>702</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>53.86281290803823</v>
+        <v>47.78393557500978</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>14.53676380771368</v>
+        <v>11.94388674133031</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.353802600455429</v>
+        <v>1.770105206786588</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0340977763625149</v>
+        <v>-0.6803068097880622</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1441</v>
+        <v>1467</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>379.6131405933369</v>
+        <v>403.514878698703</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>60.85164086674762</v>
+        <v>49.79791558324446</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>27.14591578979126</v>
+        <v>14.24138842203314</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.777105268279392</v>
+        <v>1.025422679737074</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.101811869774594</v>
+        <v>0.0424425947076083</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1503</v>
+        <v>1439</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>379.1151906356008</v>
+        <v>398.24404797791</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>199.5</v>
+        <v>0</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.66852622854098</v>
+        <v>6.524392468775801</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>8.410616441815556</v>
+        <v>23.47364507282484</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.332300541392411</v>
+        <v>0.0005140823513192</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.2341836928662539</v>
+        <v>-1.817468256396455</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1533</v>
+        <v>1538</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>370.2102463243024</v>
+        <v>397.7748644808254</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>30.55</v>
+        <v>8.85</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45.95351433744914</v>
+        <v>58.87870619618048</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>14.10011411037962</v>
+        <v>13.07584004193485</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.721063062002436</v>
+        <v>1.195814262751199</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0754617323403408</v>
+        <v>0.7997680818012148</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1321</v>
+        <v>1339</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>363.41848994332</v>
+        <v>395.3913699803809</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>32.45</v>
+        <v>42.45</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.22830081839857</v>
+        <v>43.94046768595263</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>8.596621516961221</v>
+        <v>25.67834954190439</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.559556194460817</v>
+        <v>0.8072684378089459</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0183178848413664</v>
+        <v>0.0187135265469813</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1307</v>
+        <v>1340</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>351.949082231573</v>
+        <v>386.4005668189947</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>31.5</v>
+        <v>5.18</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>59.02154342780067</v>
+        <v>48.18655467200504</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12.75640447582825</v>
+        <v>11.73592108347586</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8925828464004076</v>
+        <v>1.403427619630548</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1080275242974241</v>
+        <v>-0.0031444864777457</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1529</v>
+        <v>1220</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>347.6067142958761</v>
+        <v>384.5795921759739</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>15.7</v>
+        <v>10.9</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>44.93695770551551</v>
+        <v>53.04305167601469</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20.28426469635899</v>
+        <v>20.03170139426612</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.2799974991753746</v>
+        <v>0.5587576441062392</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.09374232327951269</v>
+        <v>0.0265520308752001</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1459</v>
+        <v>1441</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>333.9388993628672</v>
+        <v>379.6131405933369</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>18.25</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>63.91172712811801</v>
+        <v>60.85164082305973</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>61.24883033917264</v>
+        <v>27.14591590948963</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.993889936286725</v>
+        <v>0.777105268279392</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.2715166589503861</v>
+        <v>0.1018118698099095</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1539</v>
+        <v>1229</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>332.4672561658195</v>
+        <v>367.7545318308783</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>15.6</v>
+        <v>39.65</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.72288193764182</v>
+        <v>39.90364236896916</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>27.60318012771626</v>
+        <v>20.7443378291729</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.354096336734891</v>
+        <v>0.6511676843270523</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0219858748427927</v>
+        <v>-0.0521318426937259</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1210</v>
+        <v>1529</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>329.1202394852446</v>
+        <v>367.6067142958761</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>51.3</v>
+        <v>15.7</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>39.11962953104088</v>
+        <v>44.93695758128114</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>26.42206060200996</v>
+        <v>20.28426475888279</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.147795528766197</v>
+        <v>0.2799974991753746</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0014907435115404</v>
+        <v>0.093742323424166</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1473</v>
+        <v>1539</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>326.9394820325153</v>
+        <v>332.4672561658195</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>19.05</v>
+        <v>15.6</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>23.77312053870888</v>
+        <v>47.7228819005116</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>41.20492751038718</v>
+        <v>27.60318013958863</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.180935376628198</v>
+        <v>1.354096336734891</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0504970904816048</v>
+        <v>0.0219858748539195</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1417</v>
+        <v>1210</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>325.7542194418242</v>
+        <v>329.1202394852446</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>8.16</v>
+        <v>51.3</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.69900284857291</v>
+        <v>39.11962931976893</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20.98748424039871</v>
+        <v>26.42206065104622</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.9401355990438756</v>
+        <v>1.147795528766197</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0205297019982216</v>
+        <v>-0.0014907434002672</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1465</v>
+        <v>1473</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>319.1053481588773</v>
+        <v>326.939482032516</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>11.6</v>
+        <v>19.05</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>41.38242082014671</v>
+        <v>23.77312015336454</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>22.47342591411417</v>
+        <v>41.20492753971352</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.3633493704209919</v>
+        <v>1.180935376628198</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0125950700867822</v>
+        <v>-0.0504970904148421</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1527</v>
+        <v>1417</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>317.1495053943724</v>
+        <v>325.7542194418243</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>32.5</v>
+        <v>8.16</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45.47993886528642</v>
+        <v>51.69900275886339</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>12.53279475109716</v>
+        <v>20.98748420955017</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.8619072369452963</v>
+        <v>0.9401355990438756</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0204061534788022</v>
+        <v>0.0205297020115738</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1414</v>
+        <v>1465</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>315.7010743360905</v>
+        <v>319.1053481588773</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>17.65</v>
+        <v>11.6</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>47.79518960560613</v>
+        <v>41.38242052315188</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>24.53646266394821</v>
+        <v>22.47342617371204</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.8740179246171276</v>
+        <v>0.3633493704209919</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.074249135811604</v>
+        <v>0.0125950701201636</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1225</v>
+        <v>1527</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>314.0705913050009</v>
+        <v>317.1495053943723</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>24.2</v>
+        <v>32.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.71856812247304</v>
+        <v>45.47993845652302</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>22.86881075890997</v>
+        <v>12.53279478669071</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.9351522135077872</v>
+        <v>0.8619072369452963</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,28 +4333,28 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0322860906558336</v>
+        <v>0.0204061536123266</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1463</v>
+        <v>1414</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>307.3252504756294</v>
+        <v>315.7010743360903</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>17.65</v>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>54.63154481968462</v>
+        <v>47.79518955234589</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.55471016255719</v>
+        <v>24.53646268315237</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.8869984363119916</v>
+        <v>0.8740179246171276</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.01752864286306</v>
+        <v>0.0742491359260213</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1442</v>
+        <v>1225</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>304.6104845043797</v>
+        <v>314.0705913050009</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>26.8</v>
+        <v>24.2</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>36.1751354105721</v>
+        <v>44.7185681390399</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>31.53740156713424</v>
+        <v>22.86881076968812</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.64612331675515</v>
+        <v>0.9351522135077872</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.3617938567823395</v>
+        <v>-0.0322860907225961</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>296.0162289521188</v>
+        <v>313.3399591520006</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>31.2</v>
+        <v>36.25</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>36.98577006175269</v>
+        <v>45.3067633023035</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>13.60122204308803</v>
+        <v>16.29187918342631</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.447362559212212</v>
+        <v>0.9242679562740194</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1887163415205803</v>
+        <v>0.0097389709384555</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1436</v>
+        <v>1463</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>293.3399591520006</v>
+        <v>307.3252504756294</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>36.25</v>
+        <v>17.65</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45.3067633023035</v>
+        <v>54.63154484914253</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>16.29187921826139</v>
+        <v>16.55471019925678</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.9242679562740194</v>
+        <v>0.8869984363119916</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.009738971116492299</v>
+        <v>0.0175286428185488</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1413</v>
+        <v>1442</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>292.9884680635582</v>
+        <v>304.6104845043778</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>26.8</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>51.42791057999528</v>
+        <v>36.17513539576776</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7.990133214217269</v>
+        <v>31.53740173867608</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.8426820634018408</v>
+        <v>0.64612331675515</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.008996174363075199</v>
+        <v>-0.361793856760086</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1229</v>
+        <v>1108</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>292.7545318308784</v>
+        <v>300.6790071311883</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>39.65</v>
+        <v>11.1</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>39.90364245826227</v>
+        <v>35.28327264782266</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>20.74433773524027</v>
+        <v>47.47612553687782</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6511676843270523</v>
+        <v>0.2511282254443017</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0521318429051438</v>
+        <v>0.0337595336524454</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1233</v>
+        <v>1537</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>291.5890591406095</v>
+        <v>298.8473239451741</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>28.05</v>
+        <v>113</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.8446074843536</v>
+        <v>29.9326147081233</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>13.21832298126171</v>
+        <v>34.55724994224251</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4844775659518422</v>
+        <v>0.7562767260086285</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0102173510002819</v>
+        <v>0.0987692264800492</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1582</v>
+        <v>1475</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>290.0355558601498</v>
+        <v>296.9869542717298</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>71.7</v>
+        <v>25.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>49.33783721916304</v>
+        <v>37.60495693279272</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>19.61904460409086</v>
+        <v>19.45743201727216</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.9250611369117112</v>
+        <v>1.017504034017034</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.2766892100858363</v>
+        <v>-0.0278006565307901</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1232</v>
+        <v>1437</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>286.333885981582</v>
+        <v>296.0162289521188</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>154</v>
+        <v>31.2</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>47.11466420905416</v>
+        <v>36.98577010397989</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11.47201158377398</v>
+        <v>13.60122204308803</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.03737556934746</v>
+        <v>0.447362559212212</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.1353582009025526</v>
+        <v>-0.1887163415762141</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1213</v>
+        <v>1413</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>285.8779654781509</v>
+        <v>292.9884680635582</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>7.31</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>51.61399989353844</v>
+        <v>51.42791063521164</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>8.768415309632914</v>
+        <v>7.990133241332005</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3490075696794223</v>
+        <v>0.8426820634018408</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0106832971955321</v>
+        <v>0.008996174363075199</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1537</v>
+        <v>1233</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>278.8473239451741</v>
+        <v>291.5890591406095</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>113</v>
+        <v>28.05</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>29.9326147081233</v>
+        <v>48.84460744428315</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>34.55724993821649</v>
+        <v>13.21832298126171</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.7562767260086285</v>
+        <v>0.4844775659518422</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.098769226368778</v>
+        <v>0.0102173510002819</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1515</v>
+        <v>1582</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>278.648702535916</v>
+        <v>290.0355558601497</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>28.4</v>
+        <v>71.7</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>38.52258794856012</v>
+        <v>49.3378371948889</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>7.921573369800368</v>
+        <v>19.61904454278539</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.5268535109506742</v>
+        <v>0.9250611369117112</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0514913461359214</v>
+        <v>0.2766892101525945</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1457</v>
+        <v>1232</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>266.7619946726708</v>
+        <v>286.333885981582</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>14.3</v>
+        <v>154</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>47.5445108415316</v>
+        <v>47.1146641640866</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17.00190004401472</v>
+        <v>11.47201158377398</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.462022695867286</v>
+        <v>1.03737556934746</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0270695418816517</v>
+        <v>-0.1353582007913123</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1516</v>
+        <v>1213</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>257.7502053361708</v>
+        <v>285.8779654781509</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>13.6</v>
+        <v>7.31</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>47.97203490754303</v>
+        <v>51.61399986169802</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>12.75585761734087</v>
+        <v>8.768415303856315</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.2596729541732547</v>
+        <v>0.3490075696794223</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0546276238444629</v>
+        <v>0.0106832972400412</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1324</v>
+        <v>1515</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>256.3064808326836</v>
+        <v>278.648702535916</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>9.92</v>
+        <v>28.4</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>43.0296706557805</v>
+        <v>38.5225880184872</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>16.2737410011538</v>
+        <v>7.921573416114217</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.492605205546096</v>
+        <v>0.5268535109506742</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.003808806703849</v>
+        <v>-0.0514913462360633</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1471</v>
+        <v>1432</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>256.1125200253957</v>
+        <v>276.0563688949628</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>9.42</v>
+        <v>15</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>45.25637854195049</v>
+        <v>48.42739893914973</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.75172441966548</v>
+        <v>10.40331111445757</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.406136487612486</v>
+        <v>0.5422242593140716</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0091447429341071</v>
+        <v>0.0067294781957217</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>255.4609391445661</v>
+        <v>266.7619946726706</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>6.15</v>
+        <v>14.3</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>32.87971476064493</v>
+        <v>47.54451069791222</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>26.25753475597465</v>
+        <v>17.00190037776082</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.039194579254809</v>
+        <v>1.462022695867286</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.008581053265695301</v>
+        <v>-0.0270695418371435</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1217</v>
+        <v>1316</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>249.4335266745324</v>
+        <v>261.3836236342547</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>9.890000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>43.63654258508565</v>
+        <v>43.68158702327039</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>15.10566568744873</v>
+        <v>17.62487649052859</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.063059862380727</v>
+        <v>0.4083021805741521</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0096590519007663</v>
+        <v>-0.0410676291520342</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1227</v>
+        <v>1516</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>246.4504728803157</v>
+        <v>257.7502053361708</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>27.7</v>
+        <v>13.6</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>36.61155372894113</v>
+        <v>47.97203490754303</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>20.08127944385662</v>
+        <v>12.75585761734087</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.8598120616333796</v>
+        <v>0.2596729541732547</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.035612520842304</v>
+        <v>0.0546276238444629</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1522</v>
+        <v>1324</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>245.4260794639647</v>
+        <v>256.3064808326836</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>25.95</v>
+        <v>9.92</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>43.05269394553941</v>
+        <v>43.0296706557805</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>19.27261031062252</v>
+        <v>16.27374105211598</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.8494265915277157</v>
+        <v>1.492605205546096</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0343241561143849</v>
+        <v>-0.0038088067149759</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1316</v>
+        <v>1471</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>241.3836236342547</v>
+        <v>256.1125200253957</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>10.35</v>
+        <v>9.42</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>43.68158692121723</v>
+        <v>45.25637857796945</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>17.62487643399024</v>
+        <v>11.75172441966548</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4083021805741521</v>
+        <v>1.406136487612486</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0410676290407639</v>
+        <v>0.0091447429452338</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1506</v>
+        <v>1460</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>236.6192058521777</v>
+        <v>255.4609391445661</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>9.630000000000001</v>
+        <v>6.15</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>39.07383450152708</v>
+        <v>32.87971473687968</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>26.27717692429635</v>
+        <v>26.25753475597465</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.208827475238623</v>
+        <v>1.039194579254809</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0120159975091608</v>
+        <v>-0.008581053265695301</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1512</v>
+        <v>1217</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>234.5512511210584</v>
+        <v>249.433526674533</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>6.28</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>50.44295680596274</v>
+        <v>43.63654176340648</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.98000412518191</v>
+        <v>15.10566591390792</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.621565636381035</v>
+        <v>1.063059862380727</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0273003527698152</v>
+        <v>-0.0096590518340023</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1435</v>
+        <v>1227</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>234.3174585986552</v>
+        <v>246.4504728803156</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>21.05</v>
+        <v>27.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>48.66827222534098</v>
+        <v>36.61155356652819</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>6.169155667601235</v>
+        <v>20.08127967620473</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.261123898605756</v>
+        <v>0.8598120616333796</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,11 +5605,11 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.1287071897969117</v>
+        <v>-0.0356125207644129</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>226.2795255492242</v>
+        <v>246.2795255492238</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>89</v>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>53.15720447877546</v>
+        <v>53.15720448550274</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>8.379626766499488</v>
+        <v>8.379626767111679</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.9858879863436792</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>1.076147705768914</v>
+        <v>1.076147705813415</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1423</v>
+        <v>1522</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>223.4667774937124</v>
+        <v>245.4260794639648</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>34.55</v>
+        <v>25.95</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>50.93567249118693</v>
+        <v>43.05269386716376</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>8.489051587078569</v>
+        <v>19.27261030874292</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3702861916667179</v>
+        <v>0.8494265915277157</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.3760626009851851</v>
+        <v>0.034324156047625</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1446</v>
+        <v>1506</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>220.6427915220372</v>
+        <v>236.6192058521777</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>13.45</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>45.74067865377359</v>
+        <v>39.07383445220541</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.56900256745675</v>
+        <v>26.27717692429635</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5665676029783019</v>
+        <v>0.208827475238623</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.007891515466934699</v>
+        <v>0.0120159975202873</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1201</v>
+        <v>1231</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>218.4824219937969</v>
+        <v>235.9813330858368</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>11.45</v>
+        <v>78</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>35.24209388378725</v>
+        <v>32.2535262988501</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>45.67450383005718</v>
+        <v>15.31550542454301</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.764629762362404</v>
+        <v>1.309688602422596</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0272235240898707</v>
+        <v>-0.0804368984227649</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1526</v>
+        <v>1438</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>217.0688603151847</v>
+        <v>235.8256945964882</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>15.05</v>
+        <v>21.75</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45.55639640967549</v>
+        <v>49.37648926152198</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18.88096410710326</v>
+        <v>8.659728111180126</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6739873378855984</v>
+        <v>0.2224273918174453</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.08613913115921371</v>
+        <v>0.0428429506667354</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1453</v>
+        <v>1512</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>216.7251382173805</v>
+        <v>234.5512511210584</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>10.95</v>
+        <v>6.28</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>47.8067072426708</v>
+        <v>50.4429567451611</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15.88227303053368</v>
+        <v>11.98000418141556</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7405979767989717</v>
+        <v>1.621565636381035</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0149899155685487</v>
+        <v>0.0273003527520119</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1256</v>
+        <v>1435</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>213.3811015821853</v>
+        <v>234.3174585986552</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>166.5</v>
+        <v>21.05</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>36.28728123831278</v>
+        <v>48.66826035964307</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>7.797363327900702</v>
+        <v>6.169156000231242</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.6407517268559813</v>
+        <v>1.261123898605756</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.07581767864978189</v>
+        <v>0.1287071848613548</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1541</v>
+        <v>1423</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>213.2637857116385</v>
+        <v>223.4667774937124</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>20.55</v>
+        <v>34.55</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>51.13194565443357</v>
+        <v>50.93567249439094</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>16.735822704874</v>
+        <v>8.489051587078571</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.20428014588214</v>
+        <v>0.3702861916667179</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.4924265036806452</v>
+        <v>0.3760626009629308</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1468</v>
+        <v>1446</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>209.3116947982042</v>
+        <v>220.6427915220369</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>13.4</v>
+        <v>13.45</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>54.36762364456867</v>
+        <v>45.74067805710465</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>9.358020516807391</v>
+        <v>17.56900323850218</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.9761524700099056</v>
+        <v>0.5665676029783019</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0238572686057121</v>
+        <v>0.007891515644969999</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1517</v>
+        <v>1201</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>201.2526370677187</v>
+        <v>218.4824219937968</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>10.4</v>
+        <v>11.45</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>43.04425559669612</v>
+        <v>35.24209369850712</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>22.36132344136397</v>
+        <v>45.67450397212456</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.9232480333005644</v>
+        <v>0.764629762362404</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0183662208843806</v>
+        <v>-0.0272235240564892</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1443</v>
+        <v>1526</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>199.3365018333647</v>
+        <v>217.0688603151847</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>23.1</v>
+        <v>15.05</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46.52138891559356</v>
+        <v>45.55639645922077</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>6.45017918423309</v>
+        <v>18.88096412316857</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.1686782823776202</v>
+        <v>0.6739873378855984</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0380063272247896</v>
+        <v>0.08613913110357629</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1538</v>
+        <v>1453</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>197.774864480827</v>
+        <v>216.7251382173805</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>8.85</v>
+        <v>10.95</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>58.87870620234165</v>
+        <v>47.80670727997512</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.07584004524506</v>
+        <v>15.88227303053368</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.195814262751199</v>
+        <v>0.7405979767989717</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.7997680817010704</v>
+        <v>0.0149899155796738</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1108</v>
+        <v>1256</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>190.6790071311882</v>
+        <v>213.3811015821853</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>11.1</v>
+        <v>166.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>35.28327285592425</v>
+        <v>36.28728122283291</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>47.47612526536272</v>
+        <v>7.797363497659092</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.2511282254443017</v>
+        <v>0.6407517268559813</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0337595335968088</v>
+        <v>0.07581767853852291</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1109</v>
+        <v>1541</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>189.2113241001236</v>
+        <v>213.2637857116385</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>13.3</v>
+        <v>20.55</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.40660470383901</v>
+        <v>51.13194565357303</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>41.6846805239428</v>
+        <v>16.73582271398904</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.3721698461879063</v>
+        <v>1.20428014588214</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0039725173585633</v>
+        <v>0.4924265037140235</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1475</v>
+        <v>1468</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>186.9869542717296</v>
+        <v>209.3116947982042</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>25.5</v>
+        <v>13.4</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>37.60495666797372</v>
+        <v>54.36762368591708</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.45743206449411</v>
+        <v>9.358020478730069</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.017504034017034</v>
+        <v>0.9761524700099056</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0278006560968319</v>
+        <v>0.0238572685834573</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1466</v>
+        <v>1517</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>180.7953262322735</v>
+        <v>201.2526370677187</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>14.55</v>
+        <v>10.4</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>39.40262402457976</v>
+        <v>43.04425557437213</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>14.62128358769743</v>
+        <v>22.36132348295898</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.13229840609388</v>
+        <v>0.9232480333005644</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0137373693129461</v>
+        <v>0.0183662208843806</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1532</v>
+        <v>1443</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>177.2363963750479</v>
+        <v>199.3365018333647</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>21.75</v>
+        <v>23.1</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>35.15927488780609</v>
+        <v>46.52138890475552</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>19.27763737970092</v>
+        <v>6.450179255791141</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.8281357726836328</v>
+        <v>0.1686782823776202</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0916769160883895</v>
+        <v>0.0380063271802816</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1525</v>
+        <v>1109</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>170.3118555064715</v>
+        <v>189.2113241001236</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>63.2</v>
+        <v>13.3</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>50.53786853866007</v>
+        <v>41.40660497767694</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14.27631962835649</v>
+        <v>41.6846805239428</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>2.112407376166314</v>
+        <v>0.3721698461879063</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.9004414717592757</v>
+        <v>0.003972517347436</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1110</v>
+        <v>1466</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>169.7013700975961</v>
+        <v>180.7953262322735</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>14.45</v>
+        <v>14.55</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>30.40707583678359</v>
+        <v>39.40262424816942</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>36.99960483723467</v>
+        <v>14.62128363460055</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.9780023240602952</v>
+        <v>1.13229840609388</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0691362192130964</v>
+        <v>-0.0137373692684388</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1432</v>
+        <v>1532</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>166.0563688949628</v>
+        <v>177.2363963750481</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>15</v>
+        <v>21.75</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>48.42739886233688</v>
+        <v>35.15927503302262</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>10.40331111445757</v>
+        <v>19.27763756428531</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.5422242593140716</v>
+        <v>0.8281357726836328</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0067294781957217</v>
+        <v>-0.0916769159882469</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1419</v>
+        <v>1525</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>165.1918663737071</v>
+        <v>170.3118555064715</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>65.7</v>
+        <v>63.2</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>47.51506908905718</v>
+        <v>50.5378685570446</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>9.798737662499558</v>
+        <v>14.27631963878114</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.2713617442084576</v>
+        <v>2.112407376166314</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0490862953847921</v>
+        <v>0.9004414715812423</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1535</v>
+        <v>1110</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>163.0226622479253</v>
+        <v>169.7013700975961</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>45.75</v>
+        <v>14.45</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>51.20757195014404</v>
+        <v>30.40707576683207</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>11.92425838639981</v>
+        <v>36.99960483588818</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.026756251147512</v>
+        <v>0.9780023240602952</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.0861370824625499</v>
+        <v>-0.0691362191908407</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1215</v>
+        <v>1419</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>161.712044812006</v>
+        <v>165.1918663737079</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>105</v>
+        <v>65.7</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>42.37454161201404</v>
+        <v>47.51506914976267</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>14.84267891581211</v>
+        <v>9.798737648340198</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.4130922020772822</v>
+        <v>0.2713617442084576</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.1861828779788947</v>
+        <v>-0.0490862954515616</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1231</v>
+        <v>1535</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>160.9813330858373</v>
+        <v>163.0226622479253</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>78</v>
+        <v>45.75</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>32.25352684416666</v>
+        <v>51.20757202929145</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>15.31550479869816</v>
+        <v>11.92425844246726</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.309688602422596</v>
+        <v>1.026756251147512</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0804368994242026</v>
+        <v>0.0861370825738164</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1410</v>
+        <v>1215</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>157.9232588689934</v>
+        <v>161.712044812006</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>23.9</v>
+        <v>105</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>39.59119756778122</v>
+        <v>42.37454172185136</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>6.07549401229857</v>
+        <v>14.84267893051046</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.2642925444447753</v>
+        <v>0.4130922020772822</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0157162158287298</v>
+        <v>-0.1861828779788947</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1530</v>
+        <v>1410</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>153.9369963576707</v>
+        <v>157.9232588689935</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>26.35</v>
+        <v>23.9</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>32.80323908914406</v>
+        <v>39.59119753743441</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>23.66604831277229</v>
+        <v>6.075493976298156</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.169718492544122</v>
+        <v>0.2642925444447753</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0040278818455991</v>
+        <v>0.0157162158398582</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1219</v>
+        <v>1536</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>151.9858894262948</v>
+        <v>156.0558157590229</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>11.25</v>
+        <v>46.55</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>44.17072131874581</v>
+        <v>42.36248555455769</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>13.88348098247289</v>
+        <v>7.437459833246968</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.5517678691548953</v>
+        <v>0.6991100266928286</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0241342657916128</v>
+        <v>0.0919355760343771</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1203</v>
+        <v>1530</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>151.8578944004994</v>
+        <v>153.9369963576709</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>43</v>
+        <v>26.35</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>45.586183569006</v>
+        <v>32.80323921675458</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>10.34768097375827</v>
+        <v>23.66604831277229</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.3812521951790615</v>
+        <v>1.169718492544122</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0098970250733158</v>
+        <v>-0.0040278818789807</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1341</v>
+        <v>1219</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>151.2142850537759</v>
+        <v>151.9858894262948</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>39.35042316530488</v>
+        <v>44.1707211614111</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>10.04564019137353</v>
+        <v>13.88348101719256</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.0178631238137769</v>
+        <v>0.5517678691548953</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-2.226004267538104</v>
+        <v>-0.0241342657582328</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1451</v>
+        <v>1203</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>150.3704378556593</v>
+        <v>151.8578944004994</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>41.52930100637435</v>
+        <v>45.58618352946886</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>19.48851330639748</v>
+        <v>10.34768101145056</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.8906849669762013</v>
+        <v>0.3812521951790615</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.0025202615464646</v>
+        <v>0.0098970250733158</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1536</v>
+        <v>1341</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>136.0558157590228</v>
+        <v>151.2142850537756</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>46.55</v>
+        <v>0</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>42.36248532411112</v>
+        <v>39.35042316686755</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>7.437459818344227</v>
+        <v>10.04564019922184</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.6991100266928286</v>
+        <v>0.0178631238137769</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.0919355761011416</v>
+        <v>-2.22600426738232</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7258,21 +7258,21 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1438</v>
+        <v>1451</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>125.8256945964882</v>
+        <v>150.3704378556593</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>21.75</v>
+        <v>17</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>49.37648932244421</v>
+        <v>41.52930095941697</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>8.659728032504393</v>
+        <v>19.48851326669536</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.2224273918174453</v>
+        <v>0.8906849669762013</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0428429506556107</v>
+        <v>0.0025202615464646</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7336,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>36.16302595056674</v>
+        <v>36.16302590818201</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>11.60924509127705</v>
+        <v>11.60924510446065</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.9325986771346172</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.0384464136903651</v>
+        <v>-0.0384464136792395</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>80.54445011575346</v>
+        <v>100.5444501157536</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>12.1</v>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>41.38729664352951</v>
+        <v>41.38729680325771</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>17.74952512675412</v>
+        <v>17.74952512675413</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>1.001581862933714</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.027563189110765</v>
+        <v>-0.0275631891441469</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7442,16 +7442,16 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>51.63874254722317</v>
+        <v>51.63874245446677</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>10.60026203644918</v>
+        <v>10.6002621311771</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.6906900909464417</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="2" t="n">
         <v>0</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.008792381122656101</v>
+        <v>-0.0087923810002574</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>62.03449980408833</v>
+        <v>62.03449980408838</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>10.7</v>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>36.35251924111554</v>
+        <v>36.35251939521135</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>17.85168802364352</v>
+        <v>17.85168802404848</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.9662723095176038</v>
